--- a/db.xlsx
+++ b/db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\OBSERVATORIO\PROJETOS\BI e Afins\Opera facil\analise-opera-facil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC61A8C-70B3-471C-A5CA-B329F94209BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B7CC24-823F-4D11-B75D-5997DA371E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
   <si>
     <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
   </si>
@@ -70,6 +70,129 @@
   </si>
   <si>
     <t>AMIGDALECTOMIA- PEDIATRICO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE VASECTOMIA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE VARICOCELE (VARICOCELECTOMIA) - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE URETROPLASTIA (RESSECÇÃO DE CORDA) - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE SALPINGECTOMIA UNI / BILATERAL - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE RESSECÇÃO ENDOSCÓPICA DE PRÓSTATA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE PROSTATECTOMIA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE POSTECTOMIA (FIMOSE) - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE PLASTICA TOTAL DO PENIS - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE OOFORECTOMIA / OOFOROPLASTIA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE MIOMECTOMIA VIDEOLAPAROSCOPICA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE MIOMECTOMIA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE LITOTRIPSIA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE LAQUEADURA TUBARIA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE LAPAROTOMIA EXPLORADORA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE INSTALAÇÃO ENDOSCÓPICA DE CATETER DUPLO J - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HISTERECTOMIA VIDEOLAPAROSCOPICA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HISTERECTOMIA TOTAL - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HIDROCELE - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HERNIORRAFIA UMBILICAL VIDEOLAPAROSCÓPICA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HERNIORRAFIA INGUINAL VIDEOLAPAROSCÓPICA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HERNIOPLASTIA RECIDIVANTE - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HERNIOPLASTIA EPIGASTRICA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HEMORROIDECTOMIA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE EXERESE DE GLÂNDULA DE BARTHOLIN / SKENE - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE EXERESE DE CISTO VAGINAL - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE ESPERMATOCELECTOMIA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE CURETAGEM SEMIOTICA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE COLPOPERINEOPLASTIA ANTERIOR E POSTERIOR - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE COLECISTECTOMIA - ADULTO</t>
+  </si>
+  <si>
+    <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+  </si>
+  <si>
+    <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+  </si>
+  <si>
+    <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
+  </si>
+  <si>
+    <t>PACOTE PRÉ-OPERATÓRIO ADULTO - PROCTOLOGISTA</t>
+  </si>
+  <si>
+    <t>PACOTE PRÉ-OPERATÓRIO ADULTO - GINECOLOGIA</t>
+  </si>
+  <si>
+    <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+  </si>
+  <si>
+    <t>PACOTE RISCO CIRURGICO PEDIÁTRICO</t>
   </si>
 </sst>
 </file>
@@ -387,10 +510,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -436,8 +559,131 @@
       <c r="O1" t="s">
         <v>13</v>
       </c>
+      <c r="P1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" t="s">
+        <v>50</v>
+      </c>
+      <c r="T1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W1" t="s">
+        <v>47</v>
+      </c>
+      <c r="X1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -482,6 +728,129 @@
       </c>
       <c r="O2" t="s">
         <v>13</v>
+      </c>
+      <c r="P2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" t="s">
+        <v>50</v>
+      </c>
+      <c r="T2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>18</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>15</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
